--- a/input/input_table.xlsx
+++ b/input/input_table.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="38">
   <si>
     <t xml:space="preserve">Biosample</t>
   </si>
@@ -28,19 +28,19 @@
     <t xml:space="preserve">Requisição - Request ID</t>
   </si>
   <si>
-    <t xml:space="preserve">Paciente – Patient name</t>
+    <t xml:space="preserve">Paciente - Patient Name</t>
   </si>
   <si>
     <t xml:space="preserve">Requisitante - Requesting Clinician</t>
   </si>
   <si>
-    <t xml:space="preserve">Origem - Referring Facility</t>
+    <t xml:space="preserve">Origem - Referring Institution</t>
   </si>
   <si>
     <t xml:space="preserve">Cartão Nacional de Saúde - National Health ID</t>
   </si>
   <si>
-    <t xml:space="preserve">Município – City</t>
+    <t xml:space="preserve">Município - City</t>
   </si>
   <si>
     <t xml:space="preserve">Data de Cadastro - Registration Date</t>
@@ -80,6 +80,60 @@
   </si>
   <si>
     <t xml:space="preserve">Laboratório responsável - Responsible Laboratory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4900-80ng-07c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nome da Paciente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nome do Requisitante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instituto Adolfo Lutz central</t>
+  </si>
+  <si>
+    <t xml:space="preserve">São Paulo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00/00/0000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F/M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nome do Profissional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Escarro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Única</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isolado Bacteriano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erica Chimara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRBIO 33046/01-D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Projeto Gen-TB PróCura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8388-80ng-07c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7011-80ng-12c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7016-10ng-12c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7017-10ng-11c</t>
   </si>
 </sst>
 </file>
@@ -285,76 +339,314 @@
       <c r="AC1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4"/>
-    </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="4"/>
-      <c r="Q3" s="4"/>
-      <c r="R3" s="4"/>
-      <c r="S3" s="4"/>
-      <c r="T3" s="4"/>
+      <c r="A2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="4" t="n">
+        <v>123456789012</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>12345678901234</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" s="4" t="n">
+        <v>1234</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="26.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="4" t="n">
+        <v>123456789012</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>12345678901234</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>1234</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="S3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="T3" s="4" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
-      <c r="T4" s="4"/>
+      <c r="A4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>123456789012</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>12345678901234</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>1234</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="R4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="S4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="T4" s="4" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="4"/>
-      <c r="P5" s="4"/>
-      <c r="Q5" s="4"/>
-      <c r="R5" s="4"/>
-      <c r="S5" s="4"/>
-      <c r="T5" s="4"/>
+      <c r="A5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>123456789012</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>12345678901234</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>1234</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="P5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="S5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="T5" s="4" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6"/>
+      <c r="A6" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>123456789012</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>12345678901234</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>1234</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="O6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="P6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="R6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="S6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="T6" s="4" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6"/>
@@ -395,15 +687,9 @@
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6"/>
     </row>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6"/>
-    </row>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6"/>
-    </row>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6"/>
-    </row>
+    <row r="1048557" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048558" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048559" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048560" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048561" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048562" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
